--- a/docs/funding/proposals/in-prep/2026-NSF-PESOSE/nsf-pesose-track1/skp/matthis_coa_template.xlsx
+++ b/docs/funding/proposals/in-prep/2026-NSF-PESOSE/nsf-pesose-track1/skp/matthis_coa_template.xlsx
@@ -1618,7 +1618,11 @@
           <t>Idehen, Endurance</t>
         </is>
       </c>
-      <c r="C64" s="72" t="n"/>
+      <c r="C64" s="72" t="inlineStr">
+        <is>
+          <t>Chorus Innovations, Austin, TX</t>
+        </is>
+      </c>
       <c r="D64" s="73" t="n"/>
       <c r="E64" s="59" t="n"/>
     </row>
@@ -1709,7 +1713,11 @@
           <t>Casals, Andres</t>
         </is>
       </c>
-      <c r="C69" s="72" t="n"/>
+      <c r="C69" s="72" t="inlineStr">
+        <is>
+          <t>Independent, Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
       <c r="D69" s="73" t="n"/>
       <c r="E69" s="59" t="n"/>
     </row>
@@ -1724,7 +1732,11 @@
           <t>Scott, Dominic</t>
         </is>
       </c>
-      <c r="C70" s="72" t="n"/>
+      <c r="C70" s="72" t="inlineStr">
+        <is>
+          <t>Independent, Toronto, Canada</t>
+        </is>
+      </c>
       <c r="D70" s="73" t="n"/>
       <c r="E70" s="59" t="n"/>
     </row>
@@ -1736,12 +1748,12 @@
       </c>
       <c r="B71" s="72" t="inlineStr">
         <is>
-          <t>Scholl, Ben</t>
+          <t>Scholl, Benjamin</t>
         </is>
       </c>
       <c r="C71" s="72" t="inlineStr">
         <is>
-          <t>CU Denver Anschutz</t>
+          <t>University of Colorado Anschutz, Aurora, CO</t>
         </is>
       </c>
       <c r="D71" s="73" t="n"/>
